--- a/input_data/admin_data/ARG/wage_ARG_1996.xlsx
+++ b/input_data/admin_data/ARG/wage_ARG_1996.xlsx
@@ -134,7 +134,7 @@
         <v>0.87999999523162842</v>
       </c>
       <c r="C3">
-        <v>352.58999633789062</v>
+        <v>352.58999633789063</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>

--- a/input_data/admin_data/ARG/wage_ARG_1996.xlsx
+++ b/input_data/admin_data/ARG/wage_ARG_1996.xlsx
@@ -134,7 +134,7 @@
         <v>0.87999999523162842</v>
       </c>
       <c r="C3">
-        <v>352.58999633789063</v>
+        <v>352.58999633789062</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
